--- a/Direct.xlsx
+++ b/Direct.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316016\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316016\Desktop\DirectSimulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B444B970-0439-4064-A458-8D59D3A69FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAA159F-F686-44CE-B842-03047D6D568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A3873204-6EBE-4608-8CFB-982EF0D2CD83}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3873204-6EBE-4608-8CFB-982EF0D2CD83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>タイトル</t>
     <phoneticPr fontId="1"/>
@@ -96,6 +97,120 @@
     <t>画像</t>
     <rPh sb="0" eb="2">
       <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シークバー（タイムライン）
+高評価数・低評価数・同接数</t>
+    <rPh sb="14" eb="17">
+      <t>コウヒョウカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>テイヒョウカスウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ドウセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コメント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リアクション
+（モデルポーズみたいな？）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リアクション２
+または、ここに同接グラフ</t>
+    <rPh sb="15" eb="17">
+      <t>ドウセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在紹介中の作品
+（映像部分・「こちら」もやる）</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>エイゾウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイムライン
+序盤+SL+中盤+SL+終盤</t>
+    <rPh sb="7" eb="9">
+      <t>ジョバン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チュウバン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL１
+ステータス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SL２
+ステータス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード一覧</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目玉タイトル制限数　上限３
+中タイトル制限数　上限　5</t>
+    <rPh sb="0" eb="2">
+      <t>メダマ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>セイゲンスウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>セイゲンスウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウゲン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -237,7 +352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,27 +374,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -291,6 +406,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,109 +733,283 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A10409B-8C6D-4FD8-94D4-49F98400D3A2}">
-  <dimension ref="B1:J16"/>
+  <dimension ref="B1:Z24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="10" t="s">
+    <row r="1" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:26" ht="26.25" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="G2" s="7" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10"/>
+      <c r="G2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B3" s="7" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="20"/>
+    </row>
+    <row r="3" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="10"/>
       <c r="G3" s="1"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="13"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="3"/>
+    </row>
+    <row r="4" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="14"/>
       <c r="G4" s="1"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="13"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="M4" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="3"/>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="14"/>
       <c r="G5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="13"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="10"/>
+    </row>
+    <row r="6" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="14"/>
       <c r="G6" s="4"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="13"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="14"/>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="13"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="14"/>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="14"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="13"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="14"/>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="13"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="14"/>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="14"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="13"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="14"/>
+    </row>
+    <row r="11" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="13"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="17"/>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="14"/>
-    </row>
-    <row r="13" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="3"/>
+    </row>
+    <row r="13" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="M13" s="12"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="3"/>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
@@ -721,8 +1022,24 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="M14" s="12"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="10"/>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
@@ -731,22 +1048,695 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M15" s="12"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="14"/>
+    </row>
+    <row r="16" spans="2:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="4"/>
-      <c r="C16" s="11"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="M16" s="12"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="14"/>
+    </row>
+    <row r="17" spans="13:26" x14ac:dyDescent="0.4">
+      <c r="M17" s="12"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="14"/>
+    </row>
+    <row r="18" spans="13:26" x14ac:dyDescent="0.4">
+      <c r="M18" s="12"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="14"/>
+    </row>
+    <row r="19" spans="13:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M19" s="15"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="17"/>
+    </row>
+    <row r="20" spans="13:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M20" s="1"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="3"/>
+    </row>
+    <row r="21" spans="13:26" x14ac:dyDescent="0.4">
+      <c r="M21" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="10"/>
+    </row>
+    <row r="22" spans="13:26" x14ac:dyDescent="0.4">
+      <c r="M22" s="12"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="14"/>
+    </row>
+    <row r="23" spans="13:26" x14ac:dyDescent="0.4">
+      <c r="M23" s="12"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="14"/>
+    </row>
+    <row r="24" spans="13:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="M24" s="15"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="B3:E13"/>
+    <mergeCell ref="M21:Z24"/>
+    <mergeCell ref="M4:R19"/>
+    <mergeCell ref="T3:W19"/>
+    <mergeCell ref="X14:Z19"/>
+    <mergeCell ref="X5:Z11"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95EB5A43-D388-4602-A90C-23E441BB824E}">
+  <dimension ref="B1:S25"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+    </row>
+    <row r="3" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="9"/>
+      <c r="S4" s="10"/>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="14"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="14"/>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="14"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="14"/>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="14"/>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="17"/>
+    </row>
+    <row r="12" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="R13" s="9"/>
+      <c r="S13" s="10"/>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="14"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="14"/>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="14"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="14"/>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="14"/>
+    </row>
+    <row r="19" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="14"/>
+    </row>
+    <row r="20" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="17"/>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B21" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="10"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="14"/>
+    </row>
+    <row r="24" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="15"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="17"/>
+    </row>
+    <row r="25" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B21:S24"/>
+    <mergeCell ref="Q4:S11"/>
+    <mergeCell ref="Q13:S20"/>
+    <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B5:O19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
